--- a/Ozrit HR data/ozrit/HR/Employee Details/Employee Verifications/Employee Verifications.xlsx
+++ b/Ozrit HR data/ozrit/HR/Employee Details/Employee Verifications/Employee Verifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\Employee Details\Employee Verifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4F4F71-C246-46ED-B789-B9ED41831C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237FCDA1-1B93-461E-B275-95B8CF4D0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
